--- a/artfynd/A 53167-2022 artfynd.xlsx
+++ b/artfynd/A 53167-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 53167-2022 artfynd.xlsx
+++ b/artfynd/A 53167-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105983450</v>
+        <v>105983881</v>
       </c>
       <c r="B2" t="n">
-        <v>5135</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96601</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,35 +686,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105930</v>
+        <v>2170</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sjöfloen, Sm</t>
+          <t>Sjöbroviken, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576966.7349717183</v>
+        <v>577034</v>
       </c>
       <c r="R2" t="n">
-        <v>6338275.32864939</v>
+        <v>6338273</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,24 +744,9 @@
           <t>2023-01-14</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-01-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,15 +773,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105983881</v>
+        <v>105985403</v>
       </c>
       <c r="B3" t="n">
-        <v>93276</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -809,21 +784,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2170</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +809,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577034.6805355361</v>
+        <v>577102</v>
       </c>
       <c r="R3" t="n">
-        <v>6338272.803510332</v>
+        <v>6338291</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,19 +842,9 @@
           <t>2023-01-14</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-01-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,15 +871,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105985403</v>
+        <v>106059846</v>
       </c>
       <c r="B4" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -940,20 +900,23 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sjöbroviken, Sm</t>
+          <t>Sjöbroviken, Finsjö, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577102.2206121697</v>
+        <v>576978</v>
       </c>
       <c r="R4" t="n">
-        <v>6338291.956437295</v>
+        <v>6338273</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,7 +945,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -992,7 +955,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Flera bestånd</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,33 +969,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>106059846</v>
+        <v>106059891</v>
       </c>
       <c r="B5" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,10 +1027,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576978.721405231</v>
+        <v>576936</v>
       </c>
       <c r="R5" t="n">
-        <v>6338273.384096866</v>
+        <v>6338239</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,11 +1073,6 @@
       <c r="AB5" t="inlineStr">
         <is>
           <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Flera bestånd</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1144,16 +1103,11 @@
         <v>106059827</v>
       </c>
       <c r="B6" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1193,10 +1147,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>576972.3030243138</v>
+        <v>576972</v>
       </c>
       <c r="R6" t="n">
-        <v>6338297.117135375</v>
+        <v>6338298</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1262,6 +1216,109 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>105983450</v>
+      </c>
+      <c r="B7" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Sjöfloen, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>576966</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6338275</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-01-14</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-01-14</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53167-2022 artfynd.xlsx
+++ b/artfynd/A 53167-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105983881</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -868,6 +878,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105985403</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -985,6 +1000,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106059846</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1097,6 +1117,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106059891</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1216,6 +1241,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106059827</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1319,8 +1349,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105983450</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>